--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t xml:space="preserve">Visit
@@ -1498,13 +1498,13 @@
     <t>Virtual encounters can be recorded in the Encounter by specifying a location reference to a location of type "kind" such as "client's home" and an encounter.class = "virtual".</t>
   </si>
   <si>
+    <t>1671: reference from PRESCRIPTION - CLINIC (#52-5)</t>
+  </si>
+  <si>
+    <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
+  </si>
+  <si>
     <t>.participation[typeCode=LOC]</t>
-  </si>
-  <si>
-    <t>1671: reference from PRESCRIPTION - CLINIC (#52-5)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
   </si>
   <si>
     <t>Encounter.location.id</t>
@@ -1982,12 +1982,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="191.1328125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="191.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2220,16 +2220,16 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>82</v>
@@ -2821,13 +2821,13 @@
         <v>82</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2941,13 +2941,13 @@
         <v>82</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -3061,13 +3061,13 @@
         <v>82</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3183,13 +3183,13 @@
         <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3298,22 +3298,22 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3419,13 +3419,13 @@
         <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3539,13 +3539,13 @@
         <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3661,19 +3661,19 @@
         <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3783,19 +3783,19 @@
         <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -3905,19 +3905,19 @@
         <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AM16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -4025,19 +4025,19 @@
         <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AM17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4143,19 +4143,19 @@
         <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AM18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4263,19 +4263,19 @@
         <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -4380,22 +4380,22 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4503,13 +4503,13 @@
         <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4621,13 +4621,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4741,13 +4741,13 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4863,13 +4863,13 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4981,13 +4981,13 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5099,13 +5099,13 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5217,19 +5217,19 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5335,13 +5335,13 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5453,13 +5453,13 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5573,13 +5573,13 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5695,13 +5695,13 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5813,13 +5813,13 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5931,13 +5931,13 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6048,22 +6048,22 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6166,22 +6166,22 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6287,19 +6287,19 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6404,22 +6404,22 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6522,22 +6522,22 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6640,16 +6640,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6758,22 +6758,22 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -6879,13 +6879,13 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6999,13 +6999,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7121,13 +7121,13 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7238,22 +7238,22 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -7359,19 +7359,19 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7474,22 +7474,22 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7592,22 +7592,22 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -7712,22 +7712,22 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -7832,22 +7832,22 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7952,22 +7952,22 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8072,22 +8072,22 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8193,13 +8193,13 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8311,13 +8311,13 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8431,13 +8431,13 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8553,13 +8553,13 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8670,22 +8670,22 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AP56" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -8791,13 +8791,13 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8909,13 +8909,13 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9029,13 +9029,13 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9149,13 +9149,13 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9267,13 +9267,13 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9387,13 +9387,13 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9509,13 +9509,13 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9627,19 +9627,19 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -9745,13 +9745,13 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9863,19 +9863,19 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AM66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="67" hidden="true">
@@ -9981,19 +9981,19 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -10103,19 +10103,19 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -10221,19 +10221,19 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -10339,19 +10339,19 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AM70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="71" hidden="true">
@@ -10457,19 +10457,19 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="72" hidden="true">
@@ -10575,19 +10575,19 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AM72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -10692,22 +10692,22 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -10813,13 +10813,13 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -10933,13 +10933,13 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11055,13 +11055,13 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11170,22 +11170,22 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AL77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AP77" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="78" hidden="true">
@@ -11293,13 +11293,13 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11531,13 +11531,13 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11646,22 +11646,22 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AM81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="82" hidden="true">
@@ -11766,16 +11766,16 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AL82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (#52) to us-core-encounter</t>
+    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to us-core-encounter</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1498,7 +1498,7 @@
     <t>Virtual encounters can be recorded in the Encounter by specifying a location reference to a location of type "kind" such as "client's home" and an encounter.class = "virtual".</t>
   </si>
   <si>
-    <t>1671: reference from PRESCRIPTION - CLINIC (#52-5)</t>
+    <t>1671: reference from PRESCRIPTION - CLINIC (52-5)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1501,7 +1501,7 @@
     <t>1671: reference from PRESCRIPTION - CLINIC (52-5)</t>
   </si>
   <si>
-    <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
+    <t>RxOut.RxOutpat.DivisionIEN,RxOut.RxOutpat.LocationIEN,RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC]</t>
@@ -1983,7 +1983,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="93.140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -712,10 +712,16 @@
     <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
   </si>
   <si>
+    <t>finished</t>
+  </si>
+  <si>
     <t>Current state of the encounter.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
+  </si>
+  <si>
+    <t>1671-1: fixed value = #finished</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -4326,7 +4332,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4344,10 +4350,10 @@
         <v>172</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4380,30 +4386,30 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4426,16 +4432,16 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4485,7 +4491,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4520,10 +4526,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4638,10 +4644,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4758,14 +4764,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4787,10 +4793,10 @@
         <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>139</v>
@@ -4845,7 +4851,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4880,10 +4886,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4942,10 +4948,10 @@
         <v>172</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4963,7 +4969,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -4998,10 +5004,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5027,10 +5033,10 @@
         <v>206</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5081,7 +5087,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5116,10 +5122,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5142,13 +5148,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5178,10 +5184,10 @@
         <v>183</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5199,7 +5205,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -5223,21 +5229,21 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5260,13 +5266,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5317,7 +5323,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5352,10 +5358,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5470,10 +5476,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5590,14 +5596,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5619,10 +5625,10 @@
         <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>139</v>
@@ -5677,7 +5683,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5712,10 +5718,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5738,13 +5744,13 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5774,10 +5780,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5795,7 +5801,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -5830,10 +5836,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5859,10 +5865,10 @@
         <v>206</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5913,7 +5919,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -5948,10 +5954,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5977,13 +5983,13 @@
         <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6012,10 +6018,10 @@
         <v>183</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6033,7 +6039,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6054,24 +6060,24 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6097,10 +6103,10 @@
         <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6127,13 +6133,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6151,7 +6157,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6172,7 +6178,7 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>160</v>
@@ -6181,15 +6187,15 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6215,10 +6221,10 @@
         <v>178</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6245,31 +6251,31 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6293,25 +6299,25 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6330,16 +6336,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6389,7 +6395,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6410,24 +6416,24 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6450,13 +6456,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6507,7 +6513,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6528,28 +6534,28 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>160</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6568,13 +6574,13 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6625,7 +6631,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6646,10 +6652,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6660,10 +6666,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6686,13 +6692,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6743,7 +6749,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6764,24 +6770,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6896,10 +6902,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7016,14 +7022,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7045,10 +7051,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>139</v>
@@ -7103,7 +7109,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7138,10 +7144,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7167,13 +7173,13 @@
         <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7202,28 +7208,28 @@
         <v>183</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7244,24 +7250,24 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7287,10 +7293,10 @@
         <v>206</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7341,7 +7347,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7365,21 +7371,21 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7402,13 +7408,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7459,7 +7465,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7480,24 +7486,24 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7520,13 +7526,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7577,7 +7583,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7598,24 +7604,24 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7641,13 +7647,13 @@
         <v>206</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7697,7 +7703,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7718,24 +7724,24 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7758,16 +7764,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7817,7 +7823,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7838,28 +7844,28 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7881,13 +7887,13 @@
         <v>178</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7916,10 +7922,10 @@
         <v>114</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7937,7 +7943,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7958,28 +7964,28 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7998,16 +8004,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8057,7 +8063,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8078,24 +8084,24 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8118,13 +8124,13 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8175,7 +8181,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8199,7 +8205,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8210,10 +8216,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8328,10 +8334,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8448,14 +8454,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8477,10 +8483,10 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>139</v>
@@ -8535,7 +8541,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8570,14 +8576,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8596,16 +8602,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8655,7 +8661,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>90</v>
@@ -8676,24 +8682,24 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8719,10 +8725,10 @@
         <v>178</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8752,10 +8758,10 @@
         <v>114</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8773,7 +8779,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8808,10 +8814,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8834,13 +8840,13 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8891,7 +8897,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8915,7 +8921,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -8926,10 +8932,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8952,16 +8958,16 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9011,7 +9017,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9035,7 +9041,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9046,10 +9052,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9072,16 +9078,16 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9131,7 +9137,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9155,7 +9161,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9166,10 +9172,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9284,10 +9290,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9404,14 +9410,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9433,10 +9439,10 @@
         <v>136</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>139</v>
@@ -9491,7 +9497,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9526,10 +9532,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9555,10 +9561,10 @@
         <v>148</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9609,7 +9615,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9639,15 +9645,15 @@
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9670,13 +9676,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9727,7 +9733,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9751,7 +9757,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9762,10 +9768,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9791,10 +9797,10 @@
         <v>178</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9824,10 +9830,10 @@
         <v>114</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -9845,7 +9851,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9869,21 +9875,21 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9909,10 +9915,10 @@
         <v>178</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9939,13 +9945,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -9963,7 +9969,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9993,15 +9999,15 @@
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10027,16 +10033,16 @@
         <v>178</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10061,13 +10067,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10085,7 +10091,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10109,21 +10115,21 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10149,10 +10155,10 @@
         <v>178</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10182,10 +10188,10 @@
         <v>114</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10203,7 +10209,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10227,21 +10233,21 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10267,10 +10273,10 @@
         <v>178</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10300,10 +10306,10 @@
         <v>114</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10321,7 +10327,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10345,21 +10351,21 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10382,13 +10388,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10439,7 +10445,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10463,21 +10469,21 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10503,10 +10509,10 @@
         <v>178</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10536,10 +10542,10 @@
         <v>114</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10557,7 +10563,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10581,21 +10587,21 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10618,16 +10624,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10677,7 +10683,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10692,16 +10698,16 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -10712,10 +10718,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10830,10 +10836,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10950,14 +10956,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10979,10 +10985,10 @@
         <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>139</v>
@@ -11037,7 +11043,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11072,10 +11078,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11098,13 +11104,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11155,7 +11161,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>90</v>
@@ -11176,24 +11182,24 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11219,13 +11225,13 @@
         <v>110</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11254,10 +11260,10 @@
         <v>172</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11275,7 +11281,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11299,7 +11305,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11310,10 +11316,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11339,13 +11345,13 @@
         <v>178</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11371,13 +11377,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11395,7 +11401,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11430,10 +11436,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11459,10 +11465,10 @@
         <v>206</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11513,7 +11519,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11537,7 +11543,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11548,10 +11554,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11574,13 +11580,13 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11631,7 +11637,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11652,24 +11658,24 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11692,16 +11698,16 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11751,7 +11757,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11772,10 +11778,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
